--- a/TestData/TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
+++ b/TestData/TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCD5AB2-2E32-4CCD-8275-D808AC5917D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE5E0F4-6EDD-4F9D-95E5-9ED2A8BC2FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId3"/>
-    <sheet name="AssociatedOpp" sheetId="4" r:id="rId4"/>
-    <sheet name="AssociatedEng" sheetId="5" r:id="rId5"/>
+    <sheet name="AppName" sheetId="6" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="7" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId5"/>
+    <sheet name="AssociatedOpp" sheetId="4" r:id="rId6"/>
+    <sheet name="AssociatedEng" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>Client</t>
   </si>
@@ -198,9 +200,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Danielle Morello</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -256,6 +255,39 @@
   </si>
   <si>
     <t>Project Padres</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Opportunities</t>
+  </si>
+  <si>
+    <t>Engagements</t>
+  </si>
+  <si>
+    <t>William Peluchiwski</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>Tombstone Permission</t>
+  </si>
+  <si>
+    <t>No Restrictions</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>Indrajeet Singh</t>
   </si>
 </sst>
 </file>
@@ -645,9 +677,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E9D164-33B9-46A0-985E-31691E847A14}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,11 +767,14 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -820,6 +858,9 @@
       </c>
       <c r="AB2" s="4" t="s">
         <v>40</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>79</v>
       </c>
       <c r="AD2" t="s">
         <v>49</v>
@@ -831,28 +872,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B348D56F-7571-4CF0-98F5-8E40348E6DD7}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C755067-F87B-4357-BCC1-0BC2E23BD904}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -861,60 +892,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50933240-8DAA-40B7-BFDF-87B184D83775}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA43E8D6-EA7D-405A-B53B-AE49A8F5D9AC}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>65</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -923,26 +917,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC126CC3-3D66-46D2-AA1F-E0F84F595000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B348D56F-7571-4CF0-98F5-8E40348E6DD7}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -951,26 +954,60 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5281F3E7-349E-4EB0-A0D7-699B714BDCE6}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50933240-8DAA-40B7-BFDF-87B184D83775}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>71</v>
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -978,13 +1015,70 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC126CC3-3D66-46D2-AA1F-E0F84F595000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5281F3E7-349E-4EB0-A0D7-699B714BDCE6}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1240,19 +1334,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1278,19 +1381,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>